--- a/光伏配储项目/电价数据/2026/霍山站.xlsx
+++ b/光伏配储项目/电价数据/2026/霍山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48216</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75558</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5400199999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5552699999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48334</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47424</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.43851</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41622</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.40857</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40626</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.42911</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47127</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12851</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.20748</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.0307</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.20643</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.03193</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.02668</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.14776</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15146</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.13715</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.04276</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.50993</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53742</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73407</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12294</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.19684</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6613600000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.86554</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47419</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19636</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.41374</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.27638</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.98661</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28209</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.47866</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43666</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68314</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7333500000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.08375</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95455</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8933300000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80059</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76146</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48362</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46475</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41773</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42764</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7174400000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.94311</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50287</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50969</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50983</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47326</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44788</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.16288</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.02327</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.08346</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.49305</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48995</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50406</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.11282</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12303</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.24931</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.04761</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.01355</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.51032</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.02333</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.59501</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.5413300000000001</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.03062</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.78284</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.25661</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.13917</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.23178</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.21469</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.23987</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.54269</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.59284</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74339</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7544099999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16156</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.25001</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13067</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8376699999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20536</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10626</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25644</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02216</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09048</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98338</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.91423</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.95765</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77959</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.88606</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.73576</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.7809</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.72641</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7595299999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42987</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44527</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33494</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51332</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49336</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48992</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44478</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43174</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21537</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.04108</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.18571</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.78034</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.46181</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.21786</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43021</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.47075</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.40341</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28548</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6211599999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64622</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.46644</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5464600000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.4834</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6111599999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48441</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61776</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.5692699999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5572699999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.71615</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.60104</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5176499999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.55138</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34235</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5147999999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.50326</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43896</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45248</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.08018</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.04715999999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.12269</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.03849</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56101</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17371</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.15773</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.12002</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.62436</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40693</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47493</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50979</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46714</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47491</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48543</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.54864</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55816</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49506</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5047900000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42698</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32138</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.08910999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.07499</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26675</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.15616</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.09409000000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13167</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.08568000000000001</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.008460000000000001</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.15863</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.15798</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.03849</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.01373</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.004019999999999999</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01874</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24015</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48744</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.5488999999999999</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.86874</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.46444</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5784600000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5367799999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.42448</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.62373</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.41789</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10214</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00507</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19676</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26148</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.02908</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.04908</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34809</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32383</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7854800000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86922</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57755</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5429400000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20695</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.43224</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45656</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.45923</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45528</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.67235</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.50696</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.6297</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.81968</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88442</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47136</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.67162</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.50144</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.05659</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8118300000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8752000000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.5194</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.91474</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.8457</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59048</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47958</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.48375</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5450199999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.48745</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44723</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37278</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.53208</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47857</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5565399999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4704100000000001</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.6196200000000001</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.44637</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.21916</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.08769</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26786</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20088</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.45104</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.43397</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.53865</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4754</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.47972</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.46595</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.46782</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.7929299999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.43684</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.95057</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48439</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.2046</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7315499999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.82353</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.68267</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.8148099999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.6044299999999999</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47753</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5286000000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.50082</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44139</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43687</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.48137</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.62018</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43648</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45883</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.48812</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45829</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.51838</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.55476</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44602</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.52643</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43263</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.47198</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.51598</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47829</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5184800000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.43264</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63462</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.5720299999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25181</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.0173</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26453</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25917</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.45239</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.6569299999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.55303</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.03061</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.55972</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.52623</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.51403</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.43321</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3723</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5237200000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.42139</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.43582</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.43302</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.43273</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.55353</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.52218</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.5642699999999999</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.44843</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.53615</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.50314</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.40581</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28336</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21414</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.06939000000000001</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.09743</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.11485</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.08183</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.08954999999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26525</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.10089</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.22971</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.08498</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25637</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12558</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05071</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.02688</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.06269</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.05436999999999999</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16029</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.07307999999999999</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.43165</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45877</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.40443</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.44311</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.5501699999999999</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.46787</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.47096</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.4609</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.5490900000000001</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.53524</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.5310499999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.53771</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46329</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42357</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41779</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.39284</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.68749</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.5724900000000001</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49905</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.48721</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.43043</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.43466</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.54837</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23433</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17254</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18218</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21366</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19425</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.26786</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.26636</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.20014</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.2524</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.22433</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25786</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.5276900000000001</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42171</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40712</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47645</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42742</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.43436</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39643</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.6397699999999999</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.42428</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43932</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45529</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.1353</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43615</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67962</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5182100000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.41497</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46481</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25951</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26283</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.1759</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.18985</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27698</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.25612</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.55413</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.4367200000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.13216</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43668</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.5820299999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48215</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46767</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.72101</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.06896</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.9087799999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.7332000000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52938</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.27053</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41064</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.68145</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.42849</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.52066</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.43884</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.47084</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.44008</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.41169</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.48077</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.44897</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.51119</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.46189</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.47251</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36927</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.6061299999999999</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.42566</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.43186</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.49376</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43581</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41803</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6755800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.09083</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.52644</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.55011</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45606</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.37538</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.60802</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.57317</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.68699</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.5589299999999999</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.5560700000000001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.55574</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.55498</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.65699</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.55586</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.54972</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.55687</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.67631</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.54896</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.67506</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.55636</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.55669</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.5444199999999999</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.94149</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.5556599999999999</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.5533899999999999</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.5569500000000001</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.5569500000000001</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.84154</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.56276</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.5767599999999999</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.55345</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.55336</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.5480700000000001</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.54876</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.55479</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.55575</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.47372</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.57866</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.56143</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.7774800000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25168</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.01326</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27416</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29355</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.05956</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21832</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20533</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27341</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.25262</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.43926</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.6764</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.52375</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.57565</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.59536</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.55433</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.5989500000000001</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.59133</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.5654199999999999</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.93421</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.29889</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.58769</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.27335</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.67655</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.86778</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.8255</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.85617</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.03196</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.74251</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.71205</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.6240399999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.6319600000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.1871</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.70632</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>1.17563</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>1.0922</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.76147</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.5704400000000001</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.69926</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.66116</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.53691</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.72724</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.05061</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1.06401</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.94659</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.02683</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.9779500000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1.05331</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.9098999999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.59012</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.9136599999999999</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.90603</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.83178</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.5834900000000001</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1.13149</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.9040499999999999</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1.12017</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.9224199999999999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.14062</v>
+      </c>
+      <c r="X133" t="n">
+        <v>1.03514</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.08199</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1.08925</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>1.55847</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>1.4489</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1.76131</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.3657</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>1.71045</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.34562</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.6503300000000001</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.58305</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.61129</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.6665399999999999</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6830499999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.74776</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.79143</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.55728</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.01051</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.09602</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.9105599999999999</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.61885</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.56625</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.5644199999999999</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65679</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7139500000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.56813</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.99874</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.60737</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.5423300000000001</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.7232499999999999</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.5561200000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>1.15367</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>1.08613</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.11204</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.9472200000000001</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1.16196</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.8642000000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>1.25015</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>1.17267</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.5753</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.35026</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.77288</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.79492</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.9635199999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.81756</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.8677699999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.6143</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.66478</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.56756</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>1.49844</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>1.4804</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1.04181</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1.12854</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.23488</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.35963</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.6298400000000001</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.61979</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1.29947</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.61151</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.9649800000000001</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1.69626</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1.12476</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1.15113</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.94853</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.89842</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.82131</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.5524</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.56137</v>
+      </c>
+      <c r="V134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.99824</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.8613200000000001</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.55526</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.56137</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>1.11209</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>1.09457</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.57492</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.85781</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.55679</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.5505599999999999</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.5749099999999999</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.57048</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.1044</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.59496</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.8732000000000001</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.58214</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.66464</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5107200000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.88348</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.9003099999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1.00359</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.6421699999999999</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.62979</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.0266</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.7147899999999999</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.71114</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.9517</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.28678</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.64335</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.02962</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03671</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.59515</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.8021</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.78914</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.8963099999999999</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5861799999999999</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1.15524</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>1.36218</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.6128899999999999</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>1.37251</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.60345</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.9386599999999999</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>1.4557</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>1.51942</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>1.51304</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>1.29084</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.89832</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>1.30901</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.57368</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1.19457</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.55568</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.93324</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.5571499999999999</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>1.13108</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>1.68662</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.5155700000000001</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>1.60636</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1.72978</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>1.66946</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>1.37108</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1.25907</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1.77283</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.47282</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1.30649</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.46578</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.35794</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1.42879</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.55727</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.98478</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1.55468</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1.30731</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.54687</v>
+      </c>
+      <c r="R135" t="n">
+        <v>1.5563</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.48085</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1.51667</v>
+      </c>
+      <c r="V135" t="n">
+        <v>1.28919</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1.49693</v>
+      </c>
+      <c r="X135" t="n">
+        <v>1.51702</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1.53711</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>1.5572</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1.6376</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.21242</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>1.42074</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.50798</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.5465099999999999</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>1.12707</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.86625</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.76478</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.26814</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.90715</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.29197</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.94578</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.46367</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25649</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.03616</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.01401</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24842</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16798</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.7170800000000001</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.6763899999999999</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.68925</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.89639</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.89234</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.66689</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.6320800000000001</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.73261</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.66284</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.54906</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.84734</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1.11758</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.87849</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>1.03169</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>1.04111</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.8219</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.51035</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.16419</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.88991</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>1.10521</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.97648</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>1.39663</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>1.4265</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>1.39237</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>1.14502</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1.11653</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.99386</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.9246</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>1.0918</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>1.63323</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>1.67552</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.9551000000000001</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>1.55332</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.8141799999999999</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>1.55477</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>1.1276</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.9275599999999999</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.88866</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.7436799999999999</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.75374</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.7464500000000001</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.77154</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1.23274</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1.21553</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.64812</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.00831</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.9023600000000001</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.93571</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W136" t="n">
+        <v>1.01195</v>
+      </c>
+      <c r="X136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>1.18604</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.53161</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>1.6777</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.47131</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.78189</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.18221</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00091</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15568</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01435</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03784000000000001</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03563</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01184</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20778</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.52385</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.47341</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.51834</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.62848</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.5502999999999999</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.54295</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.64522</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.57313</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.48846</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.72402</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.73207</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.77674</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.54647</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.54369</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.68372</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.7117</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.7908999999999999</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1.33674</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.64644</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.83582</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.65627</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.67603</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.69192</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.7249099999999999</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.65823</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.5325599999999999</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.90324</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.17825</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1.40823</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1.38602</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1.68667</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1.0686</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1.70424</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.54627</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.5696</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1.60795</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1.59036</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>1.55111</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1.46978</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.6422100000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.78077</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.9086000000000001</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.55133</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1.53755</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.08747</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87236</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.6088300000000001</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03469</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16024</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00303</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04314</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.5144</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.79498</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.8759400000000001</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5969800000000001</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.7126699999999999</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.67004</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.87727</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.17539</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.0378</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03605</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.04017</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.13662</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.64749</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.66306</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.5739500000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.83609</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.83593</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.58385</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.6950499999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1.76961</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1.34635</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1.42064</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.5828300000000001</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1.29066</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.75893</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.95957</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1.04449</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.9977699999999999</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1.20212</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1.33159</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.5761</v>
+      </c>
+      <c r="U138" t="n">
+        <v>1.30442</v>
+      </c>
+      <c r="V138" t="n">
+        <v>1.53608</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1.55183</v>
+      </c>
+      <c r="X138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>1.68453</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>1.49639</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>1.71788</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>1.42374</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.51375</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.5230900000000001</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.92825</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.60842</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.26213</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.05368</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.42499</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.10758</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.09289</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.24761</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.46943</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.48457</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49117</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5627000000000001</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.57862</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.5717000000000001</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5348099999999999</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.7031799999999999</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.72184</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.68235</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.74527</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.6260800000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.75646</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>1.20288</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1.63443</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.94179</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>1.38168</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>1.35748</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>1.1202</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.76274</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.87052</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.7952899999999999</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.86791</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.82098</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.9906699999999999</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.09823</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.97603</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.02433</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.91144</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.89362</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.86125</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.71161</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.7865800000000001</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.76218</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.76285</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.55104</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.70829</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.6755399999999999</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.54659</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.76342</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.6934199999999999</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.6880700000000001</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.69775</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.6836</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.67733</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.67741</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.72866</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.6887000000000001</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.7620800000000001</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.73173</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.76283</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.6834</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.72802</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>1.45987</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.88978</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.81471</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5999800000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.69425</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.76171</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.63167</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.5027699999999999</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.49203</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.5595399999999999</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.5963099999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.5571200000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.6137</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.50935</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.5448200000000001</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.51017</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.46531</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.6337999999999999</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40294</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.01808</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.78439</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.90216</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.56483</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.74451</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8289099999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.45585</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.59902</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1.63613</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.62705</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.14691</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.60306</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8361000000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5732699999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>1.29919</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.89773</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.6675800000000001</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.8834500000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.73854</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.58848</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.73811</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.72263</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.72573</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.54301</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1.01927</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.83443</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.92203</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.87527</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.8226100000000001</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.66743</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.79718</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.5704900000000001</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.77616</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.7735700000000001</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.76522</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.7012200000000001</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.66108</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.66711</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.66803</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.66818</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.50662</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.71256</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.69709</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.69511</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.71665</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.54572</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.82323</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.8241900000000001</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>1.03146</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.86914</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.56168</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.6442</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.55091</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.55233</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.65584</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.58024</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.5691900000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.5620299999999999</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.5471200000000001</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.55488</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.62888</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.6194700000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.5725399999999999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.67249</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.58929</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.56516</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.61191</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.6547200000000001</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.5639400000000001</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.63439</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.61741</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.7179800000000001</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.25326</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.97257</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.78813</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.9869600000000001</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.96513</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.8935599999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.7986</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.80425</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7486799999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.07217</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>1.17356</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.93841</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.81484</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.6860299999999999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.6844600000000001</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.68867</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.72038</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.46641</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.63675</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.56055</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.7446200000000001</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.55061</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.77166</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.78791</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.77412</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.67974</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.54376</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.6631699999999999</v>
+      </c>
+      <c r="N141" t="n">
+        <v>1.01108</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.54373</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.5327000000000001</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.74274</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.70499</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.7151000000000001</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.7341</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.53959</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.7912899999999999</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.53447</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.54823</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.9098200000000001</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.92323</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.57611</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.5775800000000001</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.55537</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.7196399999999999</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.43788</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.5717300000000001</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.23783</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20597</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.18912</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24465</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03233</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.16352</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02762</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01821</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.16471</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.18732</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03258</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05116</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23064</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24825</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.47067</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.59435</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.5164500000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.44063</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.5710299999999999</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.48808</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.73651</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.50369</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5960800000000001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.63644</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.5433300000000001</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.55147</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.50303</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.46158</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.5339299999999999</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.51976</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.59772</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.45866</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.50318</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.47486</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.50576</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.79191</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.54186</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5511</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.65618</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.56229</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.46565</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51736</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.47663</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.52964</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.48347</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.47155</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.45667</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.46063</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.45661</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.49197</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.46424</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.46139</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.45818</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.44678</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.45122</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.45345</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.47104</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.43243</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26451</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.14249</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23419</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.10753</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27663</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45309</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4362799999999999</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.48087</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.43892</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.44143</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.43616</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52138</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5682</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.46067</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.44685</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5259299999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.51346</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.46408</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.44956</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.49595</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.43313</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.43234</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.43709</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48455</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40444</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40684</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14653</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19979</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02274</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.02796</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.0225</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.02643</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.01223</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.06203</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.15398</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.01547</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.20109</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.23734</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08932</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.22933</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22248</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.04090999999999999</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.17635</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14794</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26426</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25911</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40913</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.43112</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42127</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43243</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5112599999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40461</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40908</v>
       </c>
     </row>
   </sheetData>
